--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -448,7 +448,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -2413,14 +2413,30 @@
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KPC-038</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+          <t>KPC-037-1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>KPC-024</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>KPC-07</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>46316</v>
+      </c>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -459,7 +459,7 @@
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
@@ -1426,7 +1426,7 @@
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Planning for Exp.</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Planning for Exp.</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Planning for Exp.</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Planning for Exp.</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="N19" s="2" t="n"/>
@@ -1674,7 +1674,7 @@
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Planning for Exp.</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Planning for Exp.</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -584,7 +584,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="N2" s="2" t="n"/>
@@ -633,7 +633,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="N3" s="2" t="n"/>
@@ -682,7 +682,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="N4" s="2" t="n"/>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -930,7 +930,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -1863,7 +1863,7 @@
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="N23" s="2" t="n"/>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2431,8 +2431,11 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>KPC-07</t>
-        </is>
+          <t>KPC-007</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>46316</v>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -10,7 +10,7 @@
     <sheet name="KPC mouse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2572,33 +2572,9 @@
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>KPC-045</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
-  <conditionalFormatting sqref="C2:C542">
+  <autoFilter ref="A1:O41"/>
+  <conditionalFormatting sqref="C2:C541">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>UPPER(C2)="M"</formula>
     </cfRule>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -10,7 +10,7 @@
     <sheet name="KPC mouse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2452,129 +2452,9 @@
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>KPC-040</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>KPC-041</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>KPC-042</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>KPC-043</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>KPC-044</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
-  <conditionalFormatting sqref="C2:C541">
+  <autoFilter ref="A1:O36"/>
+  <conditionalFormatting sqref="C2:C536">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>UPPER(C2)="M"</formula>
     </cfRule>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -10,7 +10,7 @@
     <sheet name="KPC mouse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2410,7 +2410,11 @@
       <c r="O35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>C-015</t>
+        </is>
+      </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>KPC-037-1</t>
@@ -2452,9 +2456,103 @@
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>C-015</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>KPC-038</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>KPC-024</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>KPC-007</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>C-015</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>KPC-040</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>KPC-024</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>KPC-007</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O36"/>
-  <conditionalFormatting sqref="C2:C536">
+  <autoFilter ref="A1:O38"/>
+  <conditionalFormatting sqref="C2:C538">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>UPPER(C2)="M"</formula>
     </cfRule>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2506,7 +2506,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C-015</t>
+          <t>C-016</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -10,7 +10,7 @@
     <sheet name="KPC mouse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2550,9 +2550,52 @@
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>C-015</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>KPC-063</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>KPC-024</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>KPC-007</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
-  <conditionalFormatting sqref="C2:C538">
+  <autoFilter ref="A1:O39"/>
+  <conditionalFormatting sqref="C2:C539">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>UPPER(C2)="M"</formula>
     </cfRule>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2561,7 +2561,11 @@
           <t>KPC-063</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="n">
         <v>46285</v>
       </c>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -1996,7 +1996,11 @@
       <c r="O25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C-010</t>
+        </is>
+      </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>KPC-027</t>
@@ -2026,10 +2030,16 @@
       <c r="H26" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
+      <c r="L26" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -1998,7 +1998,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>C-010</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2053,7 +2053,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>C-011</t>
+        </is>
+      </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>KPC-028</t>
@@ -2083,10 +2087,24 @@
       <c r="H27" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2035,8 +2035,16 @@
           <t>+/-</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
       <c r="L26" s="3" t="n">
         <v>46322</v>
       </c>
@@ -2114,7 +2122,11 @@
       <c r="O27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>C-011</t>
+        </is>
+      </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>KPC-030</t>
@@ -2144,10 +2156,24 @@
       <c r="H28" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2183,7 +2183,11 @@
       <c r="O28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>C-011</t>
+        </is>
+      </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>KPC-031</t>
@@ -2213,10 +2217,24 @@
       <c r="H29" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2226,7 +2244,11 @@
       <c r="O29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C-012</t>
+        </is>
+      </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>KPC-032</t>
@@ -2256,10 +2278,24 @@
       <c r="H30" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2305,7 +2305,11 @@
       <c r="O30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>KPC-033</t>
@@ -2331,10 +2335,24 @@
       <c r="H31" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2344,7 +2362,11 @@
       <c r="O31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>KPC-034</t>
@@ -2370,10 +2392,24 @@
       <c r="H32" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2419,7 +2419,11 @@
       <c r="O32" s="2" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>KPC-035</t>
@@ -2445,10 +2449,24 @@
       <c r="H33" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2458,7 +2476,11 @@
       <c r="O33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C-014</t>
+        </is>
+      </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>KPC-036</t>
@@ -2484,10 +2506,24 @@
       <c r="H34" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2533,7 +2533,11 @@
       <c r="O34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>C-014</t>
+        </is>
+      </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>KPC-037</t>
@@ -2559,10 +2563,24 @@
       <c r="H35" s="3" t="n">
         <v>46309</v>
       </c>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2606,10 +2624,24 @@
       <c r="H36" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Live</t>
@@ -2747,10 +2779,24 @@
       <c r="H39" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2685,10 +2685,24 @@
       <c r="H37" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -2746,10 +2746,24 @@
       <c r="H38" s="3" t="n">
         <v>46316</v>
       </c>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>46322</v>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Live</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -10,7 +10,7 @@
     <sheet name="KPC mouse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2833,9 +2833,70 @@
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>C-016</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>KPC-041</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>KPC-024</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>KPC-007</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>+/+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
-  <conditionalFormatting sqref="C2:C539">
+  <autoFilter ref="A1:O40"/>
+  <conditionalFormatting sqref="C2:C540">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>UPPER(C2)="M"</formula>
     </cfRule>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -10,7 +10,7 @@
     <sheet name="KPC mouse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2894,9 +2894,70 @@
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>KPC-042</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>KPC-024</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>KPC-007</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
-  <conditionalFormatting sqref="C2:C540">
+  <autoFilter ref="A1:O41"/>
+  <conditionalFormatting sqref="C2:C541">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>UPPER(C2)="M"</formula>
     </cfRule>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -10,7 +10,7 @@
     <sheet name="KPC mouse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPC mouse'!$A$1:$O$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2955,9 +2955,70 @@
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>KPC-043</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>KPC-024</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>KPC-007</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>fl/fl</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Tg/Tg</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
-  <conditionalFormatting sqref="C2:C541">
+  <autoFilter ref="A1:O42"/>
+  <conditionalFormatting sqref="C2:C542">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>UPPER(C2)="M"</formula>
     </cfRule>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2323,7 +2323,11 @@
       <c r="D31" s="3" t="n">
         <v>46277</v>
       </c>
-      <c r="E31" s="2" t="n"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>KPC-003</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
           <t>KPC-001</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2384,7 +2384,11 @@
       <c r="D32" s="3" t="n">
         <v>46277</v>
       </c>
-      <c r="E32" s="2" t="n"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>KPC-003</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>KPC-001</t>
@@ -2441,7 +2445,11 @@
       <c r="D33" s="3" t="n">
         <v>46277</v>
       </c>
-      <c r="E33" s="2" t="n"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>KPC-003</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>KPC-001</t>
@@ -2498,7 +2506,11 @@
       <c r="D34" s="3" t="n">
         <v>46277</v>
       </c>
-      <c r="E34" s="2" t="n"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>KPC-003</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>KPC-001</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -741,7 +741,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Breeding</t>
         </is>
       </c>
       <c r="N5" s="2" t="n"/>
@@ -2567,7 +2567,11 @@
       <c r="D35" s="3" t="n">
         <v>46277</v>
       </c>
-      <c r="E35" s="2" t="n"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>KPC-003</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>KPC-001</t>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -1241,7 +1241,7 @@
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Breeding</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -930,7 +930,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -989,7 +989,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -1052,7 +1052,7 @@
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N11" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -1304,7 +1304,7 @@
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -2115,7 +2115,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N27" s="2" t="n"/>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N34" s="2" t="n"/>

--- a/mouse.xlsx
+++ b/mouse.xlsx
@@ -1922,7 +1922,7 @@
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Dead</t>
         </is>
       </c>
       <c r="N35" s="2" t="n"/>
